--- a/output/05_nike_dcf_model.xlsx
+++ b/output/05_nike_dcf_model.xlsx
@@ -264,7 +264,7 @@
     <t xml:space="preserve">fraction of revenue (adjusted: before Pace restructuring charges)</t>
   </si>
   <si>
-    <t xml:space="preserve">derived from Nike's FY2027 guidance (GUIDANCE_FY2027, midpoints): adjusted EPS 1.25 x 1,484.2m diluted shares / (1 - 25% tax) - 103m non-operating income = USD 2,371m operating income, / (46,398m x (1 - 8%)) revenue = 5.55%. Script 10 repeats the steps and checks this value (output/10_guidance_margin.csv). Set 2026-10-04 at Eric's request to build the guidance into the base case; before that FY2027 sat on the straight line from FY2026's 8.2% (9.1%)</t>
+    <t xml:space="preserve">derived from Nike's FY2027 guidance (GUIDANCE_FY2027, midpoints): adjusted EPS 1.25 x 1,484.2m diluted shares / (1 - 25% tax) - 103m non-operating income = USD 2,371m operating income, / (46,398m x (1 - 8%)) revenue = 5.55%. Script 10 repeats the steps and checks this value (output/10_guidance_margin.csv). Set 2026-10-04 to build the guidance into the base case; before that FY2027 sat on the straight line from FY2026's 8.2% (9.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">FY2027_Margin</t>
